--- a/AIML IITG ROADMAP.xlsx
+++ b/AIML IITG ROADMAP.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="141">
   <si>
     <t>WEEK 1</t>
   </si>
@@ -147,6 +147,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>Hey, excited for Week 2? Often the data we deal with can have various issues like </t>
     </r>
     <r>
@@ -242,6 +247,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>Time to level up—today we tackle Linear regression with </t>
     </r>
     <r>
@@ -273,6 +283,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>Today we will be introduced to our first ever classification model, </t>
     </r>
     <r>
@@ -476,6 +491,72 @@
   <si>
     <t>Solving Issue of Model Drift</t>
   </si>
+  <si>
+    <t>WEEK 5</t>
+  </si>
+  <si>
+    <t>Welcome to the final week of Learning, next week will be Capstone Project. Today, Let us go into the foundations of Neural Networks.</t>
+  </si>
+  <si>
+    <t>Neural Networks (1-2)</t>
+  </si>
+  <si>
+    <t>Neural Networks (3-4)</t>
+  </si>
+  <si>
+    <t>Today, we'll first build an intuitive understanding of Neural Networks and implement a simple one from scratch using Python. Then, we'll explore Keras, a user-friendly deep learning library, to quickly build and train Neural Networks with minimal code.</t>
+  </si>
+  <si>
+    <t>Neural Networks from Scratch</t>
+  </si>
+  <si>
+    <t>For Practice (using Keras) - complete points 1–3 and 6</t>
+  </si>
+  <si>
+    <t>(Optional) For Practice (using Keras) - 4 and 5 are optional</t>
+  </si>
+  <si>
+    <t>Learn core Unsupervised Learning concepts like K-Means, PCA, and Anomaly Detection with these quick, beginner-friendly video explainers.</t>
+  </si>
+  <si>
+    <t>Unsupervised Learning</t>
+  </si>
+  <si>
+    <t>K-Means Clustering</t>
+  </si>
+  <si>
+    <t>PCA</t>
+  </si>
+  <si>
+    <t>Anomaly Detection</t>
+  </si>
+  <si>
+    <t>Dive into real-time Anomaly Detection with Pathway’s suspicious activity notebook and explore KNN + LSH for fast similarity search in their dedicated notebook, both with accompanying video walkthroughs.</t>
+  </si>
+  <si>
+    <t>Anamoly Detection in Real Time</t>
+  </si>
+  <si>
+    <t>Pathway Notebook on KNN+LSH</t>
+  </si>
+  <si>
+    <t>As we wrap up the course, here are three key areas to explore next: Computer Vision, Natural Language Processing, and Reinforcement Learning. These topics open the door to cutting-edge applications and advanced real-world AI systems.</t>
+  </si>
+  <si>
+    <t>Computer Vision</t>
+  </si>
+  <si>
+    <t>Natural Language Processing</t>
+  </si>
+  <si>
+    <t>Reinforcement Learning</t>
+  </si>
+  <si>
+    <t>Computer Vision in Modern World</t>
+  </si>
+  <si>
+    <t>Transformers</t>
+  </si>
 </sst>
 </file>
 
@@ -487,7 +568,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -516,6 +597,11 @@
     <font>
       <sz val="12"/>
       <color rgb="FF212529"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -1027,137 +1113,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1170,12 +1256,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1200,13 +1280,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1484,13 +1582,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -1749,7 +1840,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="E2:K84"/>
+  <dimension ref="E2:K97"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="6" max="6" width="36.7777777777778" customWidth="1"/>
@@ -1760,7 +1851,7 @@
   <sheetData>
     <row r="2" customHeight="1"/>
     <row r="6" customHeight="1"/>
-    <row r="7" ht="31.2" spans="5:10">
+    <row r="7" ht="31.2" customHeight="1" spans="5:10">
       <c r="E7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1776,7 +1867,7 @@
       <c r="I7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J7" s="9"/>
+      <c r="J7" s="7"/>
     </row>
     <row r="8" ht="30" spans="5:10">
       <c r="E8" s="2" t="s">
@@ -1791,46 +1882,46 @@
       <c r="H8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" ht="15" spans="5:10">
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="9"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" ht="15.6" customHeight="1" spans="5:10">
+      <c r="E9" s="2"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="7"/>
     </row>
     <row r="10" ht="30" spans="5:10">
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="9"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" ht="15" spans="5:10">
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" ht="15" spans="5:10">
-      <c r="E12" s="4"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="6"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12" ht="15.6" customHeight="1" spans="5:10">
+      <c r="E12" s="2"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="4"/>
       <c r="H12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="9"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="7"/>
     </row>
     <row r="13" ht="15" spans="5:10">
       <c r="E13" s="2" t="s">
@@ -1848,25 +1939,25 @@
       <c r="I13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="9"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" ht="45" spans="5:10">
-      <c r="E14" s="4"/>
+      <c r="E14" s="2"/>
       <c r="F14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="9"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="7"/>
     </row>
     <row r="15" ht="15" spans="5:10">
-      <c r="E15" s="4"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="9"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="7"/>
     </row>
     <row r="16" spans="5:10">
       <c r="E16" s="2" t="s">
@@ -1884,15 +1975,15 @@
       <c r="I16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J16" s="9"/>
-    </row>
-    <row r="17" spans="5:10">
-      <c r="E17" s="4"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="9"/>
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17" ht="15.6" customHeight="1" spans="5:10">
+      <c r="E17" s="2"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="7"/>
     </row>
     <row r="18" spans="5:10">
       <c r="E18" s="2" t="s">
@@ -1910,15 +2001,15 @@
       <c r="I18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J18" s="9"/>
+      <c r="J18" s="7"/>
     </row>
     <row r="19" spans="5:10">
-      <c r="E19" s="4"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="9"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="7"/>
     </row>
     <row r="20" ht="15.15" spans="5:10">
       <c r="E20" s="2" t="s">
@@ -1936,15 +2027,15 @@
       <c r="I20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J20" s="10"/>
+      <c r="J20" s="8"/>
     </row>
     <row r="21" ht="15.15" spans="5:10">
-      <c r="E21" s="4"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="10"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="8"/>
     </row>
     <row r="22" spans="5:10">
       <c r="E22" s="2" t="s">
@@ -1962,25 +2053,25 @@
       <c r="I22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J22" s="9"/>
+      <c r="J22" s="7"/>
     </row>
     <row r="23" spans="5:10">
-      <c r="E23" s="4"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="9"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="7"/>
     </row>
     <row r="24" ht="15" spans="5:9">
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
     </row>
     <row r="25" ht="31.2" spans="5:9">
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -2014,27 +2105,27 @@
       </c>
     </row>
     <row r="27" ht="15" spans="5:9">
-      <c r="E27" s="4"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
     </row>
     <row r="28" ht="15" spans="5:9">
-      <c r="E28" s="4"/>
-      <c r="F28" s="5"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
     </row>
     <row r="29" ht="15" spans="5:9">
-      <c r="E29" s="4"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
     </row>
     <row r="30" spans="5:9">
       <c r="E30" s="2" t="s">
@@ -2054,11 +2145,11 @@
       </c>
     </row>
     <row r="31" spans="5:9">
-      <c r="E31" s="4"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
     </row>
     <row r="32" ht="15" spans="5:9">
       <c r="E32" s="2" t="s">
@@ -2078,27 +2169,27 @@
       </c>
     </row>
     <row r="33" ht="15" spans="5:9">
-      <c r="E33" s="4"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
     </row>
     <row r="34" ht="15" spans="5:9">
-      <c r="E34" s="4"/>
-      <c r="F34" s="5"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
     </row>
     <row r="35" ht="42" customHeight="1" spans="5:9">
-      <c r="E35" s="4"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
     </row>
     <row r="36" spans="5:9">
       <c r="E36" s="2" t="s">
@@ -2118,11 +2209,11 @@
       </c>
     </row>
     <row r="37" spans="5:9">
-      <c r="E37" s="4"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
     </row>
     <row r="38" ht="30" spans="5:9">
       <c r="E38" s="2" t="s">
@@ -2142,18 +2233,18 @@
       </c>
     </row>
     <row r="39" ht="15" spans="5:9">
-      <c r="E39" s="4"/>
-      <c r="F39" s="5"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
     </row>
     <row r="40" ht="15" spans="5:9">
-      <c r="E40" s="4"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="6"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="4"/>
       <c r="H40" s="3" t="s">
         <v>62</v>
       </c>
@@ -2162,11 +2253,11 @@
       </c>
     </row>
     <row r="41" ht="15" spans="5:9">
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
     </row>
     <row r="42" ht="31.2" spans="5:9">
       <c r="E42" s="1" t="s">
@@ -2203,27 +2294,27 @@
       </c>
     </row>
     <row r="44" ht="15" spans="5:9">
-      <c r="E44" s="4"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
     </row>
     <row r="45" ht="15" spans="5:9">
-      <c r="E45" s="4"/>
-      <c r="F45" s="5"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
     </row>
     <row r="46" ht="36" customHeight="1" spans="5:9">
-      <c r="E46" s="4"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
     </row>
     <row r="47" ht="30" spans="5:9">
       <c r="E47" s="2" t="s">
@@ -2243,17 +2334,17 @@
       </c>
     </row>
     <row r="48" ht="15" spans="5:9">
-      <c r="E48" s="4"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="6"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="4"/>
     </row>
     <row r="49" ht="15" spans="5:11">
-      <c r="E49" s="4"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
         <v>74</v>
       </c>
@@ -2275,19 +2366,19 @@
       <c r="I50" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="K50" s="5"/>
+      <c r="K50" s="3"/>
     </row>
     <row r="51" ht="15" spans="5:9">
-      <c r="E51" s="4"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
     </row>
     <row r="52" ht="15" spans="5:9">
-      <c r="E52" s="4"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
       <c r="H52" s="3" t="s">
         <v>79</v>
       </c>
@@ -2313,20 +2404,20 @@
       </c>
     </row>
     <row r="54" ht="15" spans="5:9">
-      <c r="E54" s="4"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="5"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="3"/>
     </row>
     <row r="55" ht="15" spans="5:9">
-      <c r="E55" s="4"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="I55" s="5"/>
+      <c r="I55" s="3"/>
     </row>
     <row r="56" spans="5:9">
       <c r="E56" s="2" t="s">
@@ -2346,18 +2437,18 @@
       </c>
     </row>
     <row r="57" spans="5:9">
-      <c r="E57" s="4"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
     </row>
     <row r="58" ht="15" spans="5:9">
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
     </row>
     <row r="59" ht="31.2" spans="5:9">
       <c r="E59" s="1" t="s">
@@ -2394,24 +2485,24 @@
       </c>
     </row>
     <row r="61" ht="15" spans="5:9">
-      <c r="E61" s="4"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="6"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="4"/>
     </row>
     <row r="62" ht="15" spans="5:9">
-      <c r="E62" s="4"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="6"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="4"/>
     </row>
     <row r="63" ht="15" spans="5:9">
-      <c r="E63" s="4"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
       <c r="I63" s="3" t="s">
         <v>95</v>
       </c>
@@ -2434,20 +2525,20 @@
       </c>
     </row>
     <row r="65" ht="15" spans="5:9">
-      <c r="E65" s="4"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
     </row>
     <row r="66" ht="15" spans="5:9">
-      <c r="E66" s="4"/>
-      <c r="F66" s="5"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
     </row>
     <row r="67" ht="15" spans="5:9">
       <c r="E67" s="2" t="s">
@@ -2467,27 +2558,27 @@
       </c>
     </row>
     <row r="68" ht="15" spans="5:9">
-      <c r="E68" s="4"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="6"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="4"/>
     </row>
     <row r="69" ht="15" spans="5:9">
-      <c r="E69" s="4"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
       <c r="I69" s="3" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="70" ht="15" spans="5:9">
-      <c r="E70" s="4"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="6"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" ht="30" spans="5:9">
       <c r="E71" s="2" t="s">
@@ -2507,29 +2598,29 @@
       </c>
     </row>
     <row r="72" ht="15" spans="5:9">
-      <c r="E72" s="4"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="6"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="4"/>
     </row>
     <row r="73" ht="15" spans="5:9">
-      <c r="E73" s="4"/>
-      <c r="F73" s="5"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H73" s="5"/>
+      <c r="H73" s="3"/>
       <c r="I73" s="3" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="74" ht="15" spans="5:9">
-      <c r="E74" s="4"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="6"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="4"/>
     </row>
     <row r="75" ht="15" spans="5:9">
       <c r="E75" s="2" t="s">
@@ -2549,15 +2640,15 @@
       </c>
     </row>
     <row r="76" ht="15" spans="5:9">
-      <c r="E76" s="4"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
     </row>
     <row r="77" ht="30" spans="5:9">
-      <c r="E77" s="4"/>
-      <c r="F77" s="5"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>116</v>
       </c>
@@ -2569,56 +2660,209 @@
       </c>
     </row>
     <row r="78" ht="15" spans="5:9">
-      <c r="E78" s="11"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
-    </row>
-    <row r="79" ht="15" spans="5:9">
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="14"/>
-    </row>
-    <row r="80" ht="15" spans="5:9">
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="14"/>
-    </row>
-    <row r="81" ht="15" spans="5:9">
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="14"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="10"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="11"/>
+    </row>
+    <row r="79" ht="31.95" spans="5:9">
+      <c r="E79" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="H79" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="5:9">
+      <c r="E80" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="G80" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="H80" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I80" s="19"/>
+    </row>
+    <row r="81" spans="5:9">
+      <c r="E81" s="16"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="18"/>
+      <c r="H81" s="18"/>
+      <c r="I81" s="19"/>
     </row>
     <row r="82" spans="5:9">
-      <c r="E82" s="15"/>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15"/>
-      <c r="H82" s="15"/>
-      <c r="I82" s="15"/>
+      <c r="E82" s="16"/>
+      <c r="F82" s="17"/>
+      <c r="G82" s="18"/>
+      <c r="H82" s="18"/>
+      <c r="I82" s="19"/>
     </row>
     <row r="83" spans="5:9">
-      <c r="E83" s="15"/>
-      <c r="F83" s="15"/>
-      <c r="G83" s="15"/>
-      <c r="H83" s="15"/>
-      <c r="I83" s="15"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="17"/>
+      <c r="G83" s="18"/>
+      <c r="H83" s="18"/>
+      <c r="I83" s="19"/>
     </row>
     <row r="84" spans="5:9">
       <c r="E84" s="16"/>
-      <c r="F84" s="16"/>
-      <c r="G84" s="16"/>
-      <c r="H84" s="16"/>
-      <c r="I84" s="16"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="18"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="20"/>
+    </row>
+    <row r="85" spans="5:9">
+      <c r="E85" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F85" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="H85" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="I85" s="14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="86" spans="5:9">
+      <c r="E86" s="16"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="18"/>
+      <c r="H86" s="18"/>
+      <c r="I86" s="18"/>
+    </row>
+    <row r="87" ht="15.75" spans="5:9">
+      <c r="E87" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F87" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G87" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="H87" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="I87" s="14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="88" ht="14.55" spans="5:9">
+      <c r="E88" s="16"/>
+      <c r="F88" s="18"/>
+      <c r="G88" s="18"/>
+      <c r="H88" s="18"/>
+      <c r="I88" s="19"/>
+    </row>
+    <row r="89" ht="15.75" spans="5:9">
+      <c r="E89" s="16"/>
+      <c r="F89" s="18"/>
+      <c r="G89" s="18"/>
+      <c r="H89" s="18"/>
+      <c r="I89" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="90" spans="5:9">
+      <c r="E90" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F90" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="G90" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="H90" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="I90" s="19"/>
+    </row>
+    <row r="91" spans="5:9">
+      <c r="E91" s="16"/>
+      <c r="F91" s="18"/>
+      <c r="G91" s="18"/>
+      <c r="H91" s="18"/>
+      <c r="I91" s="19"/>
+    </row>
+    <row r="92" spans="5:9">
+      <c r="E92" s="16"/>
+      <c r="F92" s="18"/>
+      <c r="G92" s="18"/>
+      <c r="H92" s="18"/>
+      <c r="I92" s="19"/>
+    </row>
+    <row r="93" spans="5:9">
+      <c r="E93" s="16"/>
+      <c r="F93" s="18"/>
+      <c r="G93" s="18"/>
+      <c r="H93" s="18"/>
+      <c r="I93" s="19"/>
+    </row>
+    <row r="94" spans="5:9">
+      <c r="E94" s="16"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="18"/>
+      <c r="H94" s="18"/>
+      <c r="I94" s="20"/>
+    </row>
+    <row r="95" ht="15.75" spans="5:9">
+      <c r="E95" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F95" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="G95" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="H95" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="I95" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="96" ht="14.55" spans="5:9">
+      <c r="E96" s="16"/>
+      <c r="F96" s="18"/>
+      <c r="G96" s="19"/>
+      <c r="H96" s="19"/>
+      <c r="I96" s="18"/>
+    </row>
+    <row r="97" ht="30.75" spans="5:9">
+      <c r="E97" s="16"/>
+      <c r="F97" s="18"/>
+      <c r="G97" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H97" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="I97" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="86">
+  <mergeCells count="108">
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="E13:E15"/>
     <mergeCell ref="E16:E17"/>
@@ -2640,6 +2884,11 @@
     <mergeCell ref="E67:E70"/>
     <mergeCell ref="E71:E74"/>
     <mergeCell ref="E75:E78"/>
+    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="E87:E89"/>
+    <mergeCell ref="E90:E94"/>
+    <mergeCell ref="E95:E97"/>
     <mergeCell ref="F8:F12"/>
     <mergeCell ref="F16:F17"/>
     <mergeCell ref="F18:F19"/>
@@ -2660,6 +2909,11 @@
     <mergeCell ref="F67:F70"/>
     <mergeCell ref="F71:F74"/>
     <mergeCell ref="F75:F78"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="F87:F89"/>
+    <mergeCell ref="F90:F94"/>
+    <mergeCell ref="F95:F97"/>
     <mergeCell ref="G13:G15"/>
     <mergeCell ref="G16:G17"/>
     <mergeCell ref="G18:G19"/>
@@ -2673,6 +2927,10 @@
     <mergeCell ref="G56:G57"/>
     <mergeCell ref="G60:G63"/>
     <mergeCell ref="G67:G70"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="G87:G89"/>
+    <mergeCell ref="G90:G94"/>
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="H18:H19"/>
@@ -2689,6 +2947,10 @@
     <mergeCell ref="H64:H66"/>
     <mergeCell ref="H67:H70"/>
     <mergeCell ref="H71:H74"/>
+    <mergeCell ref="H80:H84"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="H87:H89"/>
+    <mergeCell ref="H90:H94"/>
     <mergeCell ref="I8:I12"/>
     <mergeCell ref="I13:I15"/>
     <mergeCell ref="I16:I17"/>
@@ -2703,6 +2965,10 @@
     <mergeCell ref="I53:I55"/>
     <mergeCell ref="I56:I57"/>
     <mergeCell ref="I64:I66"/>
+    <mergeCell ref="I80:I84"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="I90:I94"/>
+    <mergeCell ref="I95:I97"/>
     <mergeCell ref="J20:J21"/>
     <mergeCell ref="K49:K50"/>
   </mergeCells>
@@ -2790,6 +3056,22 @@
     <hyperlink ref="G77" r:id="rId78" display="Kaggle Intermediate microcourse" tooltip="https://www.kaggle.com/learn/intermediate-machine-learning"/>
     <hyperlink ref="H77" r:id="rId79" display="AdaBoost implementation" tooltip="https://www.kaggle.com/code/prashant111/adaboost-classifier-tutorial/notebook"/>
     <hyperlink ref="I77" r:id="rId80" display="Solving Issue of Model Drift" tooltip="https://youtu.be/L0qw29CNCEQ"/>
+    <hyperlink ref="G80" r:id="rId81" display="Neural Networks (1-2)" tooltip="https://www.youtube.com/playlist?list=PLZHQObOWTQDNU6R1_67000Dx_ZCJB-3pi"/>
+    <hyperlink ref="H80" r:id="rId81" display="Neural Networks (3-4)" tooltip="https://www.youtube.com/playlist?list=PLZHQObOWTQDNU6R1_67000Dx_ZCJB-3pi"/>
+    <hyperlink ref="G85" r:id="rId82" display="Neural Networks from Scratch" tooltip="https://www.youtube.com/watch?v=w8yWXqWQYmU"/>
+    <hyperlink ref="H85" r:id="rId83" display="For Practice (using Keras) - complete points 1–3 and 6" tooltip="https://www.kaggle.com/learn/intro-to-deep-learning"/>
+    <hyperlink ref="I85" r:id="rId83" display="(Optional) For Practice (using Keras) - 4 and 5 are optional" tooltip="https://www.kaggle.com/learn/intro-to-deep-learning"/>
+    <hyperlink ref="G87" r:id="rId84" display="Unsupervised Learning" tooltip="https://www.youtube.com/watch?v=JnnaDNNb380"/>
+    <hyperlink ref="H87" r:id="rId85" display="K-Means Clustering" tooltip="https://www.youtube.com/watch?v=4b5d3muPQmA"/>
+    <hyperlink ref="I87" r:id="rId86" display="PCA" tooltip="https://www.youtube.com/watch?v=FD4DeN81ODY"/>
+    <hyperlink ref="I89" r:id="rId87" display="Anomaly Detection" tooltip="https://www.youtube.com/watch?v=kN--TRv1UDY"/>
+    <hyperlink ref="G90" r:id="rId88" display="Anamoly Detection in Real Time" tooltip="https://pathway.com/developers/templates/etl/suspicious_activity_tumbling_window/"/>
+    <hyperlink ref="H90" r:id="rId89" display="Pathway Notebook on KNN+LSH" tooltip="https://pathway.com/developers/templates/etl/lsh_chapter1/"/>
+    <hyperlink ref="G95" r:id="rId90" display="Computer Vision" tooltip="https://www.youtube.com/watch?v=oGvHtpJMO3M"/>
+    <hyperlink ref="H95" r:id="rId91" display="Natural Language Processing" tooltip="https://www.youtube.com/watch?v=oi0JXuL19TA"/>
+    <hyperlink ref="I95" r:id="rId92" display="Reinforcement Learning" tooltip="https://youtu.be/nIgIv4IfJ6s?si=V3mCz8BYJe8Y-Ss0"/>
+    <hyperlink ref="G97" r:id="rId93" display="Computer Vision in Modern World" tooltip="https://www.youtube.com/watch?v=YOKPo-I6cgs"/>
+    <hyperlink ref="H97" r:id="rId94" display="Transformers" tooltip="https://youtu.be/SZorAJ4I-sA?si=dwU63VUrpLWpdDOT"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
